--- a/iFST_local_OpenSesame/ifst_files/instructions.xlsx
+++ b/iFST_local_OpenSesame/ifst_files/instructions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/iFST/iFST_local_PsychoPy/ifst_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/iFST/iFST_local_OpenSesame/ifst_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{08A17812-2941-4608-8582-45425C42F179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F61517FC-D78C-4244-9B2A-E1AF84091710}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{08A17812-2941-4608-8582-45425C42F179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16655E18-768A-49A6-B313-7E12579CCA05}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -135,24 +135,6 @@
     <t>left</t>
   </si>
   <si>
-    <t>images/seq_right.png</t>
-  </si>
-  <si>
-    <t>images/seq_left.png</t>
-  </si>
-  <si>
-    <t>images/seq_simple_right.png</t>
-  </si>
-  <si>
-    <t>images/seq_complex_right.png</t>
-  </si>
-  <si>
-    <t>images/seq_execution_right.png</t>
-  </si>
-  <si>
-    <t>images/seq_imagery_right.png</t>
-  </si>
-  <si>
     <t>image_h</t>
   </si>
   <si>
@@ -171,9 +153,6 @@
 Throughout the task, please maintain your hand in this position.</t>
   </si>
   <si>
-    <t>images/seq_simple_left.png</t>
-  </si>
-  <si>
     <t>inst_msg_EN</t>
   </si>
   <si>
@@ -181,15 +160,6 @@
   </si>
   <si>
     <t>inst_pic</t>
-  </si>
-  <si>
-    <t>images/seq_complex_left.png</t>
-  </si>
-  <si>
-    <t>images/seq_execution_left.png</t>
-  </si>
-  <si>
-    <t>images/seq_imagery_left.png</t>
   </si>
   <si>
     <t>In this task you will type or imagine typing two 8-digit sequences with your RIGHT hand. Sometimes you will PHYSICALLY type the sequence. Other times you will only IMAGINE typing the sequence. During imagery, you will be asked to focus on BOTH the: 
@@ -391,6 +361,36 @@
 VISUELLE Aspekte der Bewegung (d. h. sich vorzustellen, wie Sie Ihre Finger aus einer INTERNEN Perspektive bzw. aus der ICH-PERSPEKTIVE bewegen)
 KINÄSTHETISCHE Aspekte der Bewegung (d. h. sich vorzustellen, wie sich das Zussammenziehen Ihrer Muskeln und Bewegen Ihrer Gelenke anfühlt)
 Bitte versuchen Sie immer, sich auf BEIDE ASPEKTE GLEICHZEITIG zu konzentrieren, auch wenn sich dies nicht natürlich anfühlt. Falls Ihnen dies schwergefallen ist, haben Sie nach der Aufgabe die Möglichkeit, Ihre Erfahrung zu erläutern.</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_right.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_left.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_simple_right.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_simple_left.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_complex_right.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_complex_left.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_execution_right.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_execution_left.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_imagery_right.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_imagery_left.png</t>
   </si>
 </sst>
 </file>
@@ -475,12 +475,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,7 +802,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.26953125" customWidth="1"/>
     <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.08984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.08984375" bestFit="1" customWidth="1"/>
@@ -818,405 +814,405 @@
         <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="3">
+        <v>-0.3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="I4" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E5" s="3">
+        <v>-0.3</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
+      <c r="B6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="3">
         <v>0.5</v>
       </c>
-      <c r="D4">
+      <c r="D6" s="3">
         <v>0.4</v>
       </c>
-      <c r="E4">
-        <v>-0.3</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>0.5</v>
-      </c>
-      <c r="D5">
-        <v>0.4</v>
-      </c>
-      <c r="E5">
-        <v>-0.3</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="145" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>0.5</v>
-      </c>
-      <c r="D6">
-        <v>0.4</v>
-      </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>-0.3</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="145" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7">
+      <c r="B7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3">
         <v>0.5</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>0.4</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <v>-0.3</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
+      <c r="B8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="3">
         <v>0.5</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="3">
         <v>0.4</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="3">
         <v>-0.3</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9">
+      <c r="B9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="3">
         <v>0.5</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="3">
         <v>0.4</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="3">
         <v>-0.3</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
+      <c r="B10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="3">
         <v>0.6</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="3">
         <v>0.5</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="3">
         <v>-0.3</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11">
+      <c r="B11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="3">
         <v>0.6</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="3">
         <v>0.5</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="3">
         <v>-0.3</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12">
+      <c r="B12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="3">
         <v>0.6</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="3">
         <v>0.5</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="3">
         <v>-0.3</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13">
+      <c r="B13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="3">
         <v>0.6</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="3">
         <v>0.5</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="3">
         <v>-0.3</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14">
+      <c r="B14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="3">
         <v>0</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1233,6 +1229,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9F5CAB0486A994CA2C3B13E059EF2AE" ma:contentTypeVersion="0" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8645ec4a60d0c8c7009d2d6675847a91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636d7205651659ec4fcda0bcbde9384b">
     <xsd:element name="properties">
@@ -1346,33 +1357,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1393,9 +1381,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>